--- a/public/CuentasCuentas/Devengado-CuentasCuentasSeguidas.xlsx
+++ b/public/CuentasCuentas/Devengado-CuentasCuentasSeguidas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\CuentasCuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6774A7B5-C103-4C66-807F-B422C7C6B500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B00D0B-7D47-42AF-A804-3465D5D7A010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="88">
   <si>
     <t>cuenta</t>
   </si>
@@ -240,6 +240,66 @@
   </si>
   <si>
     <t>VII.1.1 (OTROS INGRESOS Y BENEFICIOS)</t>
+  </si>
+  <si>
+    <t>8.1.4.4.3.9.9.01.13</t>
+  </si>
+  <si>
+    <t>8.1.2.4.3.9.9.01.13</t>
+  </si>
+  <si>
+    <t>4.3.9.9.01.13</t>
+  </si>
+  <si>
+    <t>1.1.2.2.02.13</t>
+  </si>
+  <si>
+    <t>Por el devengado de ingresos por compensación bancaria de recursos propios</t>
+  </si>
+  <si>
+    <t>8.1.4.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>8.1.2.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.02</t>
+  </si>
+  <si>
+    <t>Por el devengado de ingresos por Rendimientos por cuenta productiva de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.4.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>8.1.2.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.03</t>
+  </si>
+  <si>
+    <t>Por el devengado de ingresos por Compensación bancaria de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.4.4.3.9.9.01.14</t>
+  </si>
+  <si>
+    <t>8.1.2.4.3.9.9.01.14</t>
+  </si>
+  <si>
+    <t>4.3.9.9.01.14</t>
+  </si>
+  <si>
+    <t>1.1.2.2.02.14</t>
+  </si>
+  <si>
+    <t>Por el devengado al realizarse de otros ingresos propios derivados de Comisiones por retención en prestaciones , incluye Impuesto al Valor Agregado. 1 y 2</t>
   </si>
 </sst>
 </file>
@@ -269,12 +329,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -289,9 +355,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,12 +673,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A46DBC-EF38-4A4C-B82B-A7E0178DC86F}">
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.28515625" customWidth="1"/>
-    <col min="3" max="3" width="122.7109375" customWidth="1"/>
+    <col min="3" max="3" width="150.140625" customWidth="1"/>
     <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1890,6 +1957,370 @@
         <v>4</v>
       </c>
     </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>68</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D92" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>69</v>
+      </c>
+      <c r="B93" t="s">
+        <v>67</v>
+      </c>
+      <c r="C93" t="s">
+        <v>72</v>
+      </c>
+      <c r="D93" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>68</v>
+      </c>
+      <c r="B94" t="s">
+        <v>67</v>
+      </c>
+      <c r="C94" t="s">
+        <v>72</v>
+      </c>
+      <c r="D94" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>70</v>
+      </c>
+      <c r="B95" t="s">
+        <v>67</v>
+      </c>
+      <c r="C95" t="s">
+        <v>72</v>
+      </c>
+      <c r="D95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>68</v>
+      </c>
+      <c r="B96" t="s">
+        <v>67</v>
+      </c>
+      <c r="C96" t="s">
+        <v>72</v>
+      </c>
+      <c r="D96" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>71</v>
+      </c>
+      <c r="B97" t="s">
+        <v>67</v>
+      </c>
+      <c r="C97" t="s">
+        <v>72</v>
+      </c>
+      <c r="D97" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>73</v>
+      </c>
+      <c r="B98" t="s">
+        <v>67</v>
+      </c>
+      <c r="C98" t="s">
+        <v>77</v>
+      </c>
+      <c r="D98" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>74</v>
+      </c>
+      <c r="B99" t="s">
+        <v>67</v>
+      </c>
+      <c r="C99" t="s">
+        <v>77</v>
+      </c>
+      <c r="D99" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>73</v>
+      </c>
+      <c r="B100" t="s">
+        <v>67</v>
+      </c>
+      <c r="C100" t="s">
+        <v>77</v>
+      </c>
+      <c r="D100" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>75</v>
+      </c>
+      <c r="B101" t="s">
+        <v>67</v>
+      </c>
+      <c r="C101" t="s">
+        <v>77</v>
+      </c>
+      <c r="D101" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>73</v>
+      </c>
+      <c r="B102" t="s">
+        <v>67</v>
+      </c>
+      <c r="C102" t="s">
+        <v>77</v>
+      </c>
+      <c r="D102" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>76</v>
+      </c>
+      <c r="B103" t="s">
+        <v>67</v>
+      </c>
+      <c r="C103" t="s">
+        <v>77</v>
+      </c>
+      <c r="D103" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>78</v>
+      </c>
+      <c r="B104" t="s">
+        <v>67</v>
+      </c>
+      <c r="C104" t="s">
+        <v>82</v>
+      </c>
+      <c r="D104" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>79</v>
+      </c>
+      <c r="B105" t="s">
+        <v>67</v>
+      </c>
+      <c r="C105" t="s">
+        <v>82</v>
+      </c>
+      <c r="D105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>78</v>
+      </c>
+      <c r="B106" t="s">
+        <v>67</v>
+      </c>
+      <c r="C106" t="s">
+        <v>82</v>
+      </c>
+      <c r="D106" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>80</v>
+      </c>
+      <c r="B107" t="s">
+        <v>67</v>
+      </c>
+      <c r="C107" t="s">
+        <v>82</v>
+      </c>
+      <c r="D107" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>78</v>
+      </c>
+      <c r="B108" t="s">
+        <v>67</v>
+      </c>
+      <c r="C108" t="s">
+        <v>82</v>
+      </c>
+      <c r="D108" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>81</v>
+      </c>
+      <c r="B109" t="s">
+        <v>67</v>
+      </c>
+      <c r="C109" t="s">
+        <v>82</v>
+      </c>
+      <c r="D109" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>83</v>
+      </c>
+      <c r="B110" t="s">
+        <v>67</v>
+      </c>
+      <c r="C110" t="s">
+        <v>87</v>
+      </c>
+      <c r="D110" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>84</v>
+      </c>
+      <c r="B111" t="s">
+        <v>67</v>
+      </c>
+      <c r="C111" t="s">
+        <v>87</v>
+      </c>
+      <c r="D111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>83</v>
+      </c>
+      <c r="B112" t="s">
+        <v>67</v>
+      </c>
+      <c r="C112" t="s">
+        <v>87</v>
+      </c>
+      <c r="D112" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>85</v>
+      </c>
+      <c r="B113" t="s">
+        <v>67</v>
+      </c>
+      <c r="C113" t="s">
+        <v>87</v>
+      </c>
+      <c r="D113" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>83</v>
+      </c>
+      <c r="B114" t="s">
+        <v>67</v>
+      </c>
+      <c r="C114" t="s">
+        <v>87</v>
+      </c>
+      <c r="D114" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>16</v>
+      </c>
+      <c r="B115" t="s">
+        <v>67</v>
+      </c>
+      <c r="C115" t="s">
+        <v>87</v>
+      </c>
+      <c r="D115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>83</v>
+      </c>
+      <c r="B116" t="s">
+        <v>67</v>
+      </c>
+      <c r="C116" t="s">
+        <v>87</v>
+      </c>
+      <c r="D116" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>86</v>
+      </c>
+      <c r="B117" t="s">
+        <v>67</v>
+      </c>
+      <c r="C117" t="s">
+        <v>87</v>
+      </c>
+      <c r="D117" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/CuentasCuentas/Devengado-CuentasCuentasSeguidas.xlsx
+++ b/public/CuentasCuentas/Devengado-CuentasCuentasSeguidas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\CuentasCuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B00D0B-7D47-42AF-A804-3465D5D7A010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C306C1E-0583-4DFD-A0BB-43949D3854A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -242,61 +242,61 @@
     <t>VII.1.1 (OTROS INGRESOS Y BENEFICIOS)</t>
   </si>
   <si>
-    <t>8.1.4.4.3.9.9.01.13</t>
-  </si>
-  <si>
-    <t>8.1.2.4.3.9.9.01.13</t>
-  </si>
-  <si>
-    <t>4.3.9.9.01.13</t>
+    <t>8.1.4.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>8.1.2.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.02</t>
+  </si>
+  <si>
+    <t>Por el devengado de ingresos por Rendimientos por cuenta productiva de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.4.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>8.1.2.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.03</t>
+  </si>
+  <si>
+    <t>Por el devengado de ingresos por Compensación bancaria de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.4.4.3.1.9.01.02</t>
+  </si>
+  <si>
+    <t>8.1.2.4.3.1.9.01.02</t>
+  </si>
+  <si>
+    <t>4.3.1.9.01.02</t>
+  </si>
+  <si>
+    <t>1.1.2.9.02</t>
+  </si>
+  <si>
+    <t>Por el devengado de ingresos por compensación bancaria de recursos propios</t>
+  </si>
+  <si>
+    <t>8.1.4.4.1.7.1.02.02</t>
+  </si>
+  <si>
+    <t>8.1.2.4.1.7.1.02.02</t>
+  </si>
+  <si>
+    <t>4.1.7.1.02.02</t>
   </si>
   <si>
     <t>1.1.2.2.02.13</t>
-  </si>
-  <si>
-    <t>Por el devengado de ingresos por compensación bancaria de recursos propios</t>
-  </si>
-  <si>
-    <t>8.1.4.4.2.1.2.01.18</t>
-  </si>
-  <si>
-    <t>8.1.2.4.2.1.2.01.18</t>
-  </si>
-  <si>
-    <t>4.2.1.2.01.18</t>
-  </si>
-  <si>
-    <t>1.1.2.2.04.02</t>
-  </si>
-  <si>
-    <t>Por el devengado de ingresos por Rendimientos por cuenta productiva de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
-  </si>
-  <si>
-    <t>8.1.4.4.2.1.2.01.19</t>
-  </si>
-  <si>
-    <t>8.1.2.4.2.1.2.01.19</t>
-  </si>
-  <si>
-    <t>4.2.1.2.01.19</t>
-  </si>
-  <si>
-    <t>1.1.2.2.04.03</t>
-  </si>
-  <si>
-    <t>Por el devengado de ingresos por Compensación bancaria de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
-  </si>
-  <si>
-    <t>8.1.4.4.3.9.9.01.14</t>
-  </si>
-  <si>
-    <t>8.1.2.4.3.9.9.01.14</t>
-  </si>
-  <si>
-    <t>4.3.9.9.01.14</t>
-  </si>
-  <si>
-    <t>1.1.2.2.02.14</t>
   </si>
   <si>
     <t>Por el devengado al realizarse de otros ingresos propios derivados de Comisiones por retención en prestaciones , incluye Impuesto al Valor Agregado. 1 y 2</t>
@@ -329,18 +329,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -355,10 +349,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1961,10 +1954,10 @@
       <c r="A92" t="s">
         <v>68</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="B92" t="s">
+        <v>67</v>
+      </c>
+      <c r="C92" t="s">
         <v>72</v>
       </c>
       <c r="D92" t="s">
